--- a/docs/Mapping_casi_uso/matrimoni/Matr_011.xlsx
+++ b/docs/Mapping_casi_uso/matrimoni/Matr_011.xlsx
@@ -803,7 +803,7 @@
     <t>evento.datiEventoMatrimonio.padreSposo</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,3)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(2,4,5)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposo,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(0,2,4,5)</t>
   </si>
   <si>
     <t>Padre Sposa</t>
@@ -812,7 +812,7 @@
     <t>evento.datiEventoMatrimonio.padreSposa</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,2)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(2,4,5)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposa,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(0,2,4,5)</t>
   </si>
   <si>
     <t>Madre Sposo</t>
@@ -821,7 +821,7 @@
     <t>evento.datiEventoMatrimonio.madreSposo</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,3)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(1,4,5)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposo,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(0,1,4,5)</t>
   </si>
   <si>
     <t>Madre Sposa</t>
@@ -830,7 +830,7 @@
     <t>evento.datiEventoMatrimonio.madreSposa</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,2)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(1,4,5)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposa,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(0,1,4,5)</t>
   </si>
   <si>
     <t>Tutore Sposo</t>
@@ -839,13 +839,13 @@
     <t>evento.datiEventoMatrimonio.assistenteLegaleSposo</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,3)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(1,2,3,5)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposo,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(0,1,2,3,5)</t>
   </si>
   <si>
     <t>Curatore Sposo</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,3)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(1,2,3,4)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposo,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(0,1,2,3,4)</t>
   </si>
   <si>
     <t>Figlio</t>
@@ -884,7 +884,7 @@
     <t>evento.datiEventoMatrimonio.nominaAssistenteLegaleSposo</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,3)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(1,2,3)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposo,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(0,1,2,3)</t>
   </si>
   <si>
     <t>Atto Nascita Figlio</t>
@@ -902,13 +902,13 @@
     <t>evento.datiEventoMatrimonio.assistenteLegaleSposa</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,2)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(1,2,3,5)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposa,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(0,1,2,3,5)</t>
   </si>
   <si>
     <t>Curatore Sposa</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,2)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(1,2,3,4)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposa,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(0,1,2,3,4)</t>
   </si>
   <si>
     <t>Assenso figlio</t>
@@ -935,7 +935,7 @@
     <t>evento.datiEventoMatrimonio.nominaAssistenteLegaleSposa</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,2)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(1,2,3)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposa,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(0,1,2,3)</t>
   </si>
   <si>
     <t>Dati Riconoscimento - Generalità discendenti - Matrimoni</t>
@@ -1058,13 +1058,13 @@
     <t>attoNotarile</t>
   </si>
   <si>
-    <t>Assistenza minore Sposo</t>
+    <t>Assistenza Sposo</t>
   </si>
   <si>
     <t>tipoAssistenteSposo</t>
   </si>
   <si>
-    <t>Assistenza minore Sposa</t>
+    <t>Assistenza Sposa</t>
   </si>
   <si>
     <t>tipoAssistenteSposa</t>
@@ -1168,7 +1168,7 @@
     <col min="4" max="4" width="68.45703125" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="32.48828125" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="27.3203125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="218.19921875" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="119.40625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10284,10 +10284,10 @@
         <v>261</v>
       </c>
       <c r="B397" s="2" t="s">
-        <v>174</v>
+        <v>150</v>
       </c>
       <c r="C397" s="2" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="D397" s="2" t="s">
         <v>262</v>
@@ -10928,10 +10928,10 @@
         <v>264</v>
       </c>
       <c r="B425" s="2" t="s">
-        <v>174</v>
+        <v>150</v>
       </c>
       <c r="C425" s="2" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="D425" s="2" t="s">
         <v>265</v>
@@ -11572,10 +11572,10 @@
         <v>267</v>
       </c>
       <c r="B453" s="2" t="s">
-        <v>174</v>
+        <v>150</v>
       </c>
       <c r="C453" s="2" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="D453" s="2" t="s">
         <v>268</v>
@@ -12216,10 +12216,10 @@
         <v>270</v>
       </c>
       <c r="B481" s="2" t="s">
-        <v>174</v>
+        <v>150</v>
       </c>
       <c r="C481" s="2" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="D481" s="2" t="s">
         <v>271</v>
@@ -12860,10 +12860,10 @@
         <v>273</v>
       </c>
       <c r="B509" s="2" t="s">
-        <v>174</v>
+        <v>150</v>
       </c>
       <c r="C509" s="2" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="D509" s="2" t="s">
         <v>274</v>
@@ -13504,10 +13504,10 @@
         <v>276</v>
       </c>
       <c r="B537" s="2" t="s">
-        <v>174</v>
+        <v>150</v>
       </c>
       <c r="C537" s="2" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="D537" s="2" t="s">
         <v>274</v>
@@ -15965,10 +15965,10 @@
         <v>294</v>
       </c>
       <c r="B644" s="2" t="s">
-        <v>174</v>
+        <v>150</v>
       </c>
       <c r="C644" s="2" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="D644" s="2" t="s">
         <v>295</v>
@@ -16609,10 +16609,10 @@
         <v>297</v>
       </c>
       <c r="B672" s="2" t="s">
-        <v>174</v>
+        <v>150</v>
       </c>
       <c r="C672" s="2" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="D672" s="2" t="s">
         <v>295</v>
@@ -18484,7 +18484,7 @@
         <v>349</v>
       </c>
       <c r="F753" s="2" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="G753" s="2" t="s">
         <v>59</v>

--- a/docs/Mapping_casi_uso/matrimoni/Matr_011.xlsx
+++ b/docs/Mapping_casi_uso/matrimoni/Matr_011.xlsx
@@ -7895,7 +7895,7 @@
         <v>196</v>
       </c>
       <c r="C293" s="2" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="D293" s="2" t="s">
         <v>213</v>
